--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-3.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FAF722C-DE10-4F74-B80A-619E3B1F656F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3FB9603-960D-4660-9977-16E473192D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{356722E2-E0F1-471A-AC0A-E3907684556E}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{4E869704-AE87-4846-83D9-FA41DA6D2955}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="119" r:id="rId3"/>
+    <pivotCache cacheId="151" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576888773146" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{D287F5F9-2418-488F-BDBF-438466A6C53D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.57946064815" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{CBBB0F24-C718-4CEB-BD0F-B647D78D66C9}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D408EB88-FC1C-483A-B455-04549D3ADF66}" name="AllErrorPivot" cacheId="119" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A87698B9-6716-4ACB-B1DB-B612D37DC8F5}" name="AllErrorPivot" cacheId="151" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{180B2BEA-2A7B-4A7D-BF08-6DBB12DBBC75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51FC7D6-3A6F-4DA1-B101-E5898DBDF6C4}">
   <dimension ref="A4:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339CDA7F-BF0D-444F-B4B9-E17A2BC88BD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56F163D-AC18-4EEC-9943-9460F7249D29}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
